--- a/output/07_北塩原村第10期_集計仕様書.xlsx
+++ b/output/07_北塩原村第10期_集計仕様書.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方針・凡例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ニーズ調査 集計一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="在宅調査 集計一覧" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="派生変数" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クロス集計定義" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="データレイアウト" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="方針・凡例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ニーズ調査 集計一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="在宅調査 集計一覧" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="派生変数" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="クロス集計定義" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="データレイアウト" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ニーズ調査 集計一覧'!$A$3:$J$83</definedName>
@@ -200,10 +200,10 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -634,7 +634,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>■ 集計の基本方針</t>
+          <t>■ 集計の基本方針（11項目）</t>
         </is>
       </c>
     </row>
@@ -810,406 +810,613 @@
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>■ 集計軸（クロス集計の区分）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>コード</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>軸</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>適用</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>全体</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>全回答者</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>両調査</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>北山／大塩／桧原／裏磐梯</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>両調査</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>年齢階級</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>65〜74歳／75〜84歳／85歳以上</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>両調査</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>分母は設問ごとの有効回答に統一</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>構成比の分母は、その設問に回答した票の数（有効回答）とします。回収票の総数で割った値と混在させません。クロス表では行・列の双方に回答した票を分母とし、表ごとに分母を明記します（クロス集計定義シートの「分母」欄）。同じ指標に2通りの分母が現れないようにします。</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>同じ指標を複数の設問から作らない</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>1つの指標は1つの設問から作ります。やむを得ず複数の設問から作る場合は、どちらを主とするかを決めて「主指標」「補足指標」と明示し、本文・図表・目標値のすべてで主指標の値を用います。補足指標を主指標と並べて示す場合は、出所と分母が異なることを注記します。</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>表ごとに分母とn数を書く</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>すべての表に分母の定義（何に回答した票か）とn数を記載します。n&lt;30 の区分は参考値である旨を付し、単独の根拠としません（方針5）。時点の異なる値を足して合計としません。足す必要がある場合は参考値として別に示します。</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>■ 主指標と補足指標（方針10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>主指標（出所・分母）</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>補足指標（出所・分母）</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>なぜ分けるか</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="9" t="n"/>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>性別</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>男性／女性</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>両調査</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
+          <t>社会参加・通いの場への参加</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>主：村の実績（地域包括支援センター運営状況調査）。分母は65歳以上人口</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>補：アンケート P01（問5(1)で月1〜3回以上）。分母は問5(1)の有効回答</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>母集団が違う。村の実績は全高齢者、アンケートは回答者のみ。交付金の評価指標と計画の目標値は村の実績による</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
       <c r="A21" s="9" t="n"/>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>認定状況</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>認定なし／要支援1・2／要介護1・2／要介護3〜5</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>認定データとの紐付けが前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
+          <t>要介護度</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>主：名簿・要介護認定データ（CERT）</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>補：在宅調査A票の自己申告</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>自己申告は区分の取り違えが生じる。クロス集計の軸には名簿の値を用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
       <c r="A22" s="9" t="n"/>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>世帯類型</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>単身／夫婦のみ／その他</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>両調査</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
+          <t>在宅生活の継続に必要な支援</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>主：在宅調査A票 問12。分母は同設問の有効回答</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>補：ニーズ調査 問7(11)（今後必要な支援）。分母は同設問の有効回答</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>対象者が違う。前者は在宅の要介護認定者、後者は一般高齢者を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
       <c r="A23" s="9" t="n"/>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>前回比較</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>第9期調査（令和4年8月版）との対比</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>設問文・選択肢が同一のもののみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
+          <t>低栄養の状態</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>主：R04（低栄養リスク。問3の判定）</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>補：B01（BMI。問8の身長・体重から算出）</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>R04は国の手引きの判定で見える化に登録する。BMIは補足の記述にとどめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="9" t="n"/>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>生活機能4層</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>元気・活躍層／元気・未参加層／リスク層／要支援・要介護層</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>派生変数 L01</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>要介護度</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>要支援1・2／要介護1・2／要介護3〜5</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>在宅調査のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="9" t="n"/>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>介護者の勤務形態</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>フルタイム／パートタイム／働いていない</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>在宅調査のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>■ シートの構成</t>
+          <t>認知症の相談窓口の認知</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>主：ニーズ調査 問9(2)。分母は同設問の有効回答</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>単一の設問による。第9期（31.2%・令和5年度）との比較に用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>■ 集計軸（クロス集計の区分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>コード</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>軸</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>適用</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>全体</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>全回答者</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>両調査</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="9" t="n"/>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>ニーズ調査 集計一覧</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>80設問。設問ごとの集計方法とクロス軸</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>北山／大塩／桧原／裏磐梯</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>両調査</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="9" t="n"/>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>在宅調査 集計一覧</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>26設問。A票・B票</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>年齢階級</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>65〜74歳／75〜84歳／85歳以上</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>両調査</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="9" t="n"/>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>派生変数</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>20件。リスク判定・合成変数の定義</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>男性／女性</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>両調査</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="9" t="n"/>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>クロス集計定義</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>20件。分析編で作成するクロス表</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>認定状況</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>認定なし／要支援1・2／要介護1・2／要介護3〜5</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>認定データとの紐付けが前提</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="9" t="n"/>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>世帯類型</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>単身／夫婦のみ／その他</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>両調査</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>前回比較</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>第9期調査（令和4年8月版）との対比</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>設問文・選択肢が同一のもののみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="9" t="n"/>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>生活機能4層</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>元気・活躍層／元気・未参加層／リスク層／要支援・要介護層</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>派生変数 L01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>要介護度</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>要支援1・2／要介護1・2／要介護3〜5</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>在宅調査のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>介護者の勤務形態</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>フルタイム／パートタイム／働いていない</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>在宅調査のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>■ シートの構成</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>ニーズ調査 集計一覧</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>80設問。設問ごとの集計方法とクロス軸</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>在宅調査 集計一覧</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>26設問。A票・B票</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>派生変数</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>20件。リスク判定・合成変数の定義</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>クロス集計定義</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>20件。分析編で作成するクロス表</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="9" t="n"/>
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>データレイアウト</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>入力データの列構成</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="B35" s="12" t="inlineStr">
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>※ 設問数の内訳：ニーズ調査 必須34・オプション32・村独自14（枝番を1設問として数えた場合）。手引きの「必須35問／オプション30問」とは数え方が異なります。</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="B36" s="12" t="inlineStr">
+    <row r="47" ht="24" customHeight="1">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>※ 派生変数のリスク判定の該当基準には【要確認】を付しています。手引きに明記があるのはBMI 18.5以下のみで、他は見える化システムの算出方法との突合が必要です（確認事項K-91）。</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="B37" s="12" t="inlineStr">
+    <row r="48" ht="24" customHeight="1">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>※ ★印は分析編（doc24 第Ⅱ部）で中心的に用いる設問・クロス表です。</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="B38" s="12" t="inlineStr">
+    <row r="49" ht="24" customHeight="1">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>※ 村独自設問は見える化への登録対象外（「−」）です。集計は行いますが全国・県との比較はできません。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="26">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
-    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B46:F46"/>
     <mergeCell ref="D7:F7"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B48:F48"/>
     <mergeCell ref="D12:F12"/>
-    <mergeCell ref="C30:F30"/>
     <mergeCell ref="D9:F9"/>
-    <mergeCell ref="C33:F33"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="C44:F44"/>
     <mergeCell ref="D10:F10"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="C43:F43"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B26:F26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1303,50 +1510,50 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="10" t="n">
+      <c r="A4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>問1</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>家族構成をお教えください</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,E,F,G,H</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>環境因子。単身世帯の規模は見守り施策の基礎</t>
         </is>
@@ -1403,50 +1610,50 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>問1</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>(2)①</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>介護・介助が必要になった主な原因</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>複数</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>単純集計＋上位5位</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>健康状態。(2)で「1．必要ない」以外の方のみ</t>
         </is>
@@ -1503,50 +1710,50 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>問1</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>現在の暮らしの状況を経済的にどう感じていますか</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,E,F,G,H</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>環境因子。有償の支え合いの前提条件</t>
         </is>
@@ -1603,50 +1810,50 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>問2</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>階段を手すりや壁をつたわらずに昇っていますか</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,G</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>心身機能・運動器。派生 R01</t>
         </is>
@@ -1703,50 +1910,50 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>問2</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>15分位続けて歩いていますか</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,G</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>心身機能・運動器。派生 R01</t>
         </is>
@@ -1803,50 +2010,50 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>問2</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>転倒に対する不安は大きいですか</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,G</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>心身機能・転倒。派生 R02</t>
         </is>
@@ -1903,50 +2110,50 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>問2</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>(7)</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>昨年と比べて外出の回数が減っていますか</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,G</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t>活動。派生 R03</t>
         </is>
@@ -2003,50 +2210,50 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>問2</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>(8)①</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>外出を控えている理由</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>複数</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>単純集計＋地区別</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,E,F,G,H</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>★地区差が大きいと想定。移動支援施策の根拠。(8)で「1．はい」の方のみ</t>
         </is>
@@ -2103,50 +2310,50 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>問3</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>身長・体重</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>数値</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>BMIを算出（体重kg÷（身長m）^2）</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>個人因子。派生 R04。18.5以下で低栄養が疑われる（手引き明記）</t>
         </is>
@@ -2203,50 +2410,50 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>問3</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>お茶や汁物等でむせることがありますか</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,G</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>心身機能・口腔。派生 R05</t>
         </is>
@@ -2303,50 +2510,50 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>問3</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>歯磨きを毎日していますか</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>個人因子</t>
         </is>
@@ -2403,50 +2610,50 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>問3</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>(6)①</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>噛み合わせは良いですか</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr">
         <is>
           <t>心身機能・口腔。派生 R05</t>
         </is>
@@ -2503,50 +2710,50 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>問3</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>(7)</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>6か月間で2〜3kg以上の体重減少がありましたか</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,G</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>個人因子。派生 R04</t>
         </is>
@@ -2703,50 +2910,50 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>問4</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>物忘れが多いと感じますか</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,G</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I32" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>心身機能・認知。派生 R06</t>
         </is>
@@ -2803,50 +3010,50 @@
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>問4</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>今日が何月何日かわからない時がありますか</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,G</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I34" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>心身機能・認知。派生 R06</t>
         </is>
@@ -2903,50 +3110,50 @@
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>問4</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>自分で食品・日用品の買物をしていますか</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,G</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I36" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>活動・IADL。派生 R07</t>
         </is>
@@ -3003,50 +3210,50 @@
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="10" t="n">
+      <c r="A38" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>問4</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>(7)</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>自分で請求書の支払いをしていますか</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,G</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>活動・IADL。派生 R07</t>
         </is>
@@ -3103,50 +3310,50 @@
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>問4</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>(9)</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>年金などの書類が書けますか</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
@@ -3203,50 +3410,50 @@
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="10" t="n">
+      <c r="A42" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>問4</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>(11)</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>本や雑誌を読んでいますか</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G42" s="11" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H42" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I42" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr">
+      <c r="J42" s="10" t="inlineStr">
         <is>
           <t>活動・知的能動性。派生 R08</t>
         </is>
@@ -3303,50 +3510,50 @@
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="10" t="n">
+      <c r="A44" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>問4</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>(13)</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>友人の家を訪ねていますか</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H44" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I44" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>活動・社会的役割。派生 R09</t>
         </is>
@@ -3403,50 +3610,50 @@
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="10" t="n">
+      <c r="A46" s="11" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>問4</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>(15)</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>病人を見舞うことができますか</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G46" s="11" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I46" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>活動・社会的役割。派生 R09</t>
         </is>
@@ -3503,50 +3710,50 @@
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="10" t="n">
+      <c r="A48" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>問4</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>(17)</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>趣味はありますか</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>単一＋自由</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr">
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>単純集計＋自由記述の分類</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I48" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr">
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>活動。自由記述は分類コード化して上位20位を掲載</t>
         </is>
@@ -3603,50 +3810,50 @@
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="10" t="n">
+      <c r="A50" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>問5</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>会・グループ等への参加頻度（8種類）</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>マトリクス</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr">
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>項目別に単純集計＋「月1回以上参加」の合成</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,E,F,G,H</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="I50" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr">
+      <c r="J50" s="10" t="inlineStr">
         <is>
           <t>★参加。派生 P01。⑤介護予防のための通いの場は村の事業名を明記済</t>
         </is>
@@ -3703,50 +3910,50 @@
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="10" t="n">
+      <c r="A52" s="11" t="n">
         <v>49</v>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>問5</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>地域づくり活動に企画・運営として参加してみたいと思いますか</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,E,F,G,H</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I52" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="J52" s="10" t="inlineStr">
         <is>
           <t>★参加。担い手推計の中核（doc24§7-2）</t>
         </is>
@@ -3803,50 +4010,50 @@
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="10" t="n">
+      <c r="A54" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>問6</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>(1)①</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>いつ引退しましたか</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>数値</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
+      <c r="G54" s="10" t="inlineStr">
         <is>
           <t>年代別に集計</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H54" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I54" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr">
+      <c r="J54" s="10" t="inlineStr">
         <is>
           <t>(1)で「2．引退した」の方のみ</t>
         </is>
@@ -3903,50 +4110,50 @@
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="10" t="n">
+      <c r="A56" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>問7</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>心配事や愚痴を聞いてあげる人</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
+      <c r="E56" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>複数</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr">
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>単純集計＋「いない」率</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="H56" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,E,F,G,H</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I56" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J56" s="11" t="inlineStr">
+      <c r="J56" s="10" t="inlineStr">
         <is>
           <t>環境因子。派生 S02（提供）</t>
         </is>
@@ -4003,50 +4210,50 @@
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="10" t="n">
+      <c r="A58" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>問7</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>看病や世話をしてあげる人</t>
         </is>
       </c>
-      <c r="E58" s="10" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>複数</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>単純集計＋「いない」率</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="H58" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,E,F,G,H</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="I58" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J58" s="11" t="inlineStr">
+      <c r="J58" s="10" t="inlineStr">
         <is>
           <t>環境因子。派生 S02（提供）</t>
         </is>
@@ -4103,50 +4310,50 @@
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="10" t="n">
+      <c r="A60" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>問7</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D60" s="10" t="inlineStr">
         <is>
           <t>友人・知人と会う頻度</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="E60" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
+      <c r="G60" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="H60" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="I60" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J60" s="11" t="inlineStr">
+      <c r="J60" s="10" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
@@ -4203,50 +4410,50 @@
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="10" t="n">
+      <c r="A62" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>問7</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>(8)</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
         <is>
           <t>よく会う友人・知人はどんな関係の人ですか</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E62" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>複数</t>
         </is>
       </c>
-      <c r="G62" s="11" t="inlineStr">
+      <c r="G62" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H62" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr">
+      <c r="I62" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J62" s="11" t="inlineStr">
+      <c r="J62" s="10" t="inlineStr">
         <is>
           <t>環境因子</t>
         </is>
@@ -4403,50 +4610,50 @@
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="10" t="n">
+      <c r="A66" s="11" t="n">
         <v>63</v>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>問8</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D66" s="10" t="inlineStr">
         <is>
           <t>現在のあなたの健康状態はいかがですか</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
+      <c r="E66" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G66" s="11" t="inlineStr">
+      <c r="G66" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="H66" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,E,F,G,H</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="I66" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J66" s="11" t="inlineStr">
+      <c r="J66" s="10" t="inlineStr">
         <is>
           <t>健康状態。主観的健康感</t>
         </is>
@@ -4503,50 +4710,50 @@
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="10" t="n">
+      <c r="A68" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>問8</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>この1か月間、気分が沈んだりゆううつになることがありましたか</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="E68" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G68" s="11" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="H68" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,G</t>
         </is>
       </c>
-      <c r="I68" s="10" t="inlineStr">
+      <c r="I68" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J68" s="11" t="inlineStr">
+      <c r="J68" s="10" t="inlineStr">
         <is>
           <t>心身機能・うつ。派生 R10</t>
         </is>
@@ -4603,50 +4810,50 @@
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="10" t="n">
+      <c r="A70" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="B70" s="10" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>問8</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="D70" s="11" t="inlineStr">
+      <c r="D70" s="10" t="inlineStr">
         <is>
           <t>お酒は飲みますか</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr">
+      <c r="E70" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G70" s="11" t="inlineStr">
+      <c r="G70" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H70" s="10" t="inlineStr">
+      <c r="H70" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I70" s="10" t="inlineStr">
+      <c r="I70" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J70" s="11" t="inlineStr">
+      <c r="J70" s="10" t="inlineStr">
         <is>
           <t>個人因子</t>
         </is>
@@ -4703,50 +4910,50 @@
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="10" t="n">
+      <c r="A72" s="11" t="n">
         <v>69</v>
       </c>
-      <c r="B72" s="10" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>問8</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="11" t="inlineStr">
         <is>
           <t>(7)</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
         <is>
           <t>現在治療中、または後遺症のある病気はありますか</t>
         </is>
       </c>
-      <c r="E72" s="10" t="inlineStr">
+      <c r="E72" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>複数</t>
         </is>
       </c>
-      <c r="G72" s="11" t="inlineStr">
+      <c r="G72" s="10" t="inlineStr">
         <is>
           <t>単純集計＋疾病数の算出（0／1〜2／3以上）</t>
         </is>
       </c>
-      <c r="H72" s="10" t="inlineStr">
+      <c r="H72" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D,E,F,G,H</t>
         </is>
       </c>
-      <c r="I72" s="10" t="inlineStr">
+      <c r="I72" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J72" s="11" t="inlineStr">
+      <c r="J72" s="10" t="inlineStr">
         <is>
           <t>★個人因子。派生 D01。ICF分析の主軸（doc24§6-4）</t>
         </is>
@@ -4803,50 +5010,50 @@
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="10" t="n">
+      <c r="A74" s="11" t="n">
         <v>71</v>
       </c>
-      <c r="B74" s="10" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>問9</t>
         </is>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C74" s="11" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="D74" s="11" t="inlineStr">
+      <c r="D74" s="10" t="inlineStr">
         <is>
           <t>認知症の症状がある又は家族に認知症の症状がある人がいますか</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr">
+      <c r="E74" s="11" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H74" s="10" t="inlineStr">
+      <c r="H74" s="11" t="inlineStr">
         <is>
           <t>A,B,C,D</t>
         </is>
       </c>
-      <c r="I74" s="10" t="inlineStr">
+      <c r="I74" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J74" s="11" t="inlineStr">
+      <c r="J74" s="10" t="inlineStr">
         <is>
           <t>認知症施策</t>
         </is>
@@ -5500,50 +5707,50 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>A票</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>問2</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>世帯類型</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>基本</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>A,B,C,I,J</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>集計軸F</t>
         </is>
@@ -5600,50 +5807,50 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>A票</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>問4</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>ご本人の年齢</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>基本</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>集計軸として使用</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>A,B,I,J</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>集計軸C</t>
         </is>
@@ -5700,50 +5907,50 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>A票</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>問6</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>現時点での施設等への入所・入居の検討状況</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>基本</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>単純集計＋問6-1とのクロス</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>A,B,C,I,J</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>★最重要3設問の1つ。施設整備の直接の根拠</t>
         </is>
@@ -5800,50 +6007,50 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>A票</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>問7</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>現在抱えている傷病</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>複数</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>単純集計＋疾病数</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>A,B,I,J</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr"/>
+      <c r="J12" s="10" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="13" t="n">
@@ -5896,50 +6103,50 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>A票</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>問9</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>介護保険サービスの利用状況（A〜L）</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>基本</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>マトリクス</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>サービス別に利用率・利用回数の分布</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>A,B,C,I,J</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>給付実績との突合で回答の妥当性を検証</t>
         </is>
@@ -5996,50 +6203,50 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>A票</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>問11</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>現在利用している介護保険サービス以外の支援・サービス</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>複数</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>単純集計＋地区別</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>A,B,C,I,J</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t>★最重要3設問の1つ。ニーズ調査 問7(9)と対応</t>
         </is>
@@ -6096,50 +6303,50 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>A票</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>問13</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>現在、訪問診療を利用していますか</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>A,B,C,I,J</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>★doc23§2-1で復活を推奨。在宅医療・介護連携の唯一の把握手段</t>
         </is>
@@ -6196,50 +6403,50 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>B票</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>問1</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>過去1年の間に介護を理由に仕事を辞めた家族・親族はいますか</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>基本</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>複数</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>A,B,C,I,J</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>★介護離職の実績</t>
         </is>
@@ -6292,50 +6499,50 @@
       <c r="J21" s="14" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>B票</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>問3</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>主な介護者の性別</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>A,B,I,J</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="13" t="n">
@@ -6388,50 +6595,50 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>B票</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>問5</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>現在、主な介護者が行っている介護等</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>複数</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>A,B,C,I,J</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>身体介護／生活援助／その他の区分別に集計</t>
         </is>
@@ -6488,50 +6695,50 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>B票</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>問7</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>主な介護者の現在の勤務形態</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>基本</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>単一</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>集計軸として使用</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>A,B,I,J</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr">
         <is>
           <t>集計軸J</t>
         </is>
@@ -6588,50 +6795,50 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>B票</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>問9</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>勤め先からどのような支援があれば両立に効果があると思いますか</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>複数</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>単純集計＋上位5位</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>A,B,C,I,J</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>同上。3つまで選択可</t>
         </is>
@@ -7061,30 +7268,30 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>R99</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>リスク該当領域数</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>R01〜R10</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>該当したリスクの個数（0〜10）。3区分（0／1〜2／3以上）にも変換</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>合成</t>
         </is>
@@ -7121,30 +7328,30 @@
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>P01</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>社会参加あり</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>問5(1)</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>8種類のいずれかに「月1〜3回」以上参加で該当</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>合成</t>
         </is>
@@ -7181,30 +7388,30 @@
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>支え合いの提供あり</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>問7(2)(4)</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>いずれかで「そのような人はいない」以外を選択で該当</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>合成</t>
         </is>
@@ -7241,30 +7448,30 @@
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>L01</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>生活機能4層</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>R99・P01・認定状況</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>第1層＝R99が0かつP01該当／第2層＝R99が0かつP01非該当／第3層＝R99が1以上かつ認定なし／第4層＝認定あり</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>合成</t>
         </is>
@@ -7301,30 +7508,30 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>AGE</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>年齢階級</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>名簿</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>65〜74歳／75〜84歳／85歳以上</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>集計軸</t>
         </is>
@@ -7375,16 +7582,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -7394,10 +7602,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>★＝doc24 第Ⅱ部（分析編）の中核。X-01・X-02・X-03・X-04 は第2回策定委員会の資料の骨格になります。</t>
+          <t>★＝doc24 第Ⅱ部（分析編）の中核。X-01・X-02・X-03・X-04 は第2回策定委員会の資料の骨格になります。　｜　分母は表ごとに明記し、回収票の総数では割りません。「両設問」＝行・列の双方に回答した票を分母とします。</t>
         </is>
       </c>
     </row>
@@ -7434,11 +7642,16 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
+          <t>分母</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>用途・出典</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="26" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="19" t="n">
         <v>1</v>
       </c>
@@ -7469,11 +7682,16 @@
       </c>
       <c r="G4" s="20" t="inlineStr">
         <is>
+          <t>両設問（問8(7)とリスク判定10領域の双方が算出できる票）</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
           <t>★分析編の中核。doc24§6-4 表5-X</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="26" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="19" t="n">
         <v>2</v>
       </c>
@@ -7504,11 +7722,16 @@
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
+          <t>リスク判定が算出できる票（認定状況は名簿由来のため欠損なし）</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
           <t>★議事録の「元気な軽度者」の検証。doc24§6-4 表5-Y</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="26" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="19" t="n">
         <v>3</v>
       </c>
@@ -7539,11 +7762,16 @@
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
+          <t>両設問（L01が確定し、かつ問5(2)(3)に回答した票）</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
           <t>★担い手の推計。doc24§7-2</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="19" t="n">
         <v>4</v>
       </c>
@@ -7574,46 +7802,56 @@
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
+          <t>両設問（問7(1)〜(4)のすべてに回答した票）</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
           <t>★孤立層の特定。doc24§7-1</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="10" t="n">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>X-05</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>生活機能4層 × 地区</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>L01（4区分）</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>地区（4区分）</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>ニーズ</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>L01が確定した票（地区は名簿由来）</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>施策の地区別展開</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="13" t="n">
         <v>6</v>
       </c>
@@ -7642,44 +7880,54 @@
           <t>ニーズ</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>L01が確定した票（年齢は名簿由来）</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>X-07</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>孤立 × 家族構成・経済状況</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>S99</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>問1(1)(3)</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>ニーズ</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>両設問（S99が確定し、かつ問1(1)(3)に回答した票）</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>見守り施策の対象像</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="19" t="n">
         <v>8</v>
       </c>
@@ -7710,11 +7958,16 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
+          <t>設問（問2(9)の有効回答。複数回答のため合計は100%を超える）</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
           <t>★移動支援施策の根拠</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="19" t="n">
         <v>9</v>
       </c>
@@ -7745,11 +7998,16 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
+          <t>設問（問2(8)①の有効回答。外出を控えている方のみが対象）</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
           <t>★同上</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="19" t="n">
         <v>10</v>
       </c>
@@ -7780,11 +8038,16 @@
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
+          <t>設問（問7(11)の有効回答。複数回答）</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
           <t>★除雪の地区差</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="19" t="n">
         <v>11</v>
       </c>
@@ -7815,11 +8078,16 @@
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
+          <t>両設問（保険外サービスを利用している方のみが対象）</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
           <t>★有償ボランティアの実態</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="13" t="n">
         <v>12</v>
       </c>
@@ -7850,46 +8118,56 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
+          <t>両設問（問8(7)と問5(1)の双方に回答した票）</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
           <t>「疾病があっても参加できる」ことの検証</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="10" t="n">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>X-13</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>認知症相談窓口の認知 × 年齢・地区</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>問9(2)</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>AGE・地区</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>ニーズ</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>設問（問9(2)の有効回答）</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>交付金 支援目標Ⅱの弱点に対応</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="13" t="n">
         <v>14</v>
       </c>
@@ -7920,11 +8198,16 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
+          <t>設問（問10(5)の有効回答）</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
           <t>交付金 支援目標Ⅲの弱点に対応</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="19" t="n">
         <v>15</v>
       </c>
@@ -7955,11 +8238,16 @@
       </c>
       <c r="G18" s="20" t="inlineStr">
         <is>
+          <t>両設問（問6に回答し、かつ問6-1に回答した票）</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
           <t>★施設の潜在需要。doc24§5-3</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="19" t="n">
         <v>16</v>
       </c>
@@ -7975,7 +8263,7 @@
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>I（3区分）</t>
+          <t>I（2区分）</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -7990,46 +8278,56 @@
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
+          <t>B票 問10の有効回答（介護者が回答した票）。要介護度は名簿由来</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
           <t>★仕様書4Ⅰ(6)。介護離職の予備軍</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="10" t="n">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>X-17</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>介護者の勤務形態 × 不安に感じる介護</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>J（3区分）</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>B票 問6</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>在宅</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>両設問（B票 問6・問7の双方に回答した票）</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>仕事と介護の両立支援の設計</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="19" t="n">
         <v>18</v>
       </c>
@@ -8045,7 +8343,7 @@
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>I（3区分）</t>
+          <t>I（2区分）</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -8060,46 +8358,56 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
+          <t>A票 問12の有効回答</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
           <t>★共助・互助の対象範囲</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="10" t="n">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>X-19</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>要介護度 × サービス利用状況</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>I（3区分）</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>I（2区分）</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>A票 問9</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>在宅</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>A票 問9の有効回答（複数回答）</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>見込量推計の補強</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="26" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="13" t="n">
         <v>20</v>
       </c>
@@ -8130,14 +8438,19 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
+          <t>A票 問13の有効回答</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
           <t>在宅医療・介護連携</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8271,7 +8584,7 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -8281,12 +8594,12 @@
           <t>受付日</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>YYYY/MM/DD</t>
         </is>
@@ -8296,7 +8609,7 @@
           <t>受託者</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>小分け送付の受渡し記録と突合</t>
         </is>
@@ -8331,7 +8644,7 @@
       <c r="F7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -8341,12 +8654,12 @@
           <t>地区</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>北山／大塩／桧原／裏磐梯</t>
         </is>
@@ -8356,7 +8669,7 @@
           <t>名簿・問0</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>集計軸B</t>
         </is>
@@ -8395,7 +8708,7 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -8405,12 +8718,12 @@
           <t>生年月／年齢</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>数値</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>基準日（R8.9.1）時点の年齢</t>
         </is>
@@ -8420,7 +8733,7 @@
           <t>名簿</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>集計軸C。年齢階級を導出</t>
         </is>
@@ -8523,7 +8836,7 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>末尾</t>
         </is>
@@ -8533,12 +8846,12 @@
           <t>派生変数</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>数値・文字</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>R01〜R10・R99・D01・P01・S01・S02・S99・L01・B01</t>
         </is>
@@ -8548,7 +8861,7 @@
           <t>算出</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>「派生変数」シートの定義による</t>
         </is>

--- a/output/07_北塩原村第10期_集計仕様書.xlsx
+++ b/output/07_北塩原村第10期_集計仕様書.xlsx
@@ -981,7 +981,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>補：B01（BMI。問8の身長・体重から算出）</t>
+          <t>補：B01（BMI。問3(1)の身長・体重から算出）</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>要支援1・2／要介護1・2／要介護3〜5</t>
+          <t>要介護1・2／要介護3〜5（2区分）</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>在宅調査のみ</t>
+          <t>在宅調査のみ。名簿に要支援の方は含まれない（doc43）ため2区分に統一</t>
         </is>
       </c>
     </row>

--- a/output/07_北塩原村第10期_集計仕様書.xlsx
+++ b/output/07_北塩原村第10期_集計仕様書.xlsx
@@ -1150,12 +1150,12 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>認定なし／要支援1・2／要介護1・2／要介護3〜5</t>
+          <t>認定なし／事業対象者／要支援1・2／要介護1以上（4区分）</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>認定データとの紐付けが前提</t>
+          <t>認定データとの紐付けが前提。事業対象者の判別には総合事業の対象者の情報も要る。該当数10未満の区分は統合（doc16 §6）</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>第1層＝R99が0かつP01該当／第2層＝R99が0かつP01非該当／第3層＝R99が1以上かつ認定なし／第4層＝認定あり</t>
+          <t>第1層＝R99が0かつP01該当／第2層＝R99が0かつP01非該当／第3層＝R99が1以上かつ認定なし（事業対象者を含む）／第4層＝認定あり</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -7553,12 +7553,12 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>認定データ</t>
+          <t>認定データ・総合事業の対象者情報</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>認定なし／要支援1・2／要介護1・2／要介護3〜5</t>
+          <t>認定なし／事業対象者／要支援1・2／要介護1以上（4区分）。ニーズ調査の対象は一般高齢者・事業対象者・要支援認定者のため要介護1以上は少数</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">

--- a/output/07_北塩原村第10期_集計仕様書.xlsx
+++ b/output/07_北塩原村第10期_集計仕様書.xlsx
@@ -627,7 +627,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>作成：令和8年9月3日／根拠：調査票 第1稿（0828版）＋doc23の修正案＋doc24 骨子案／設問番号は doc23 の修正（ニーズ問7(7)の復活・在宅問13の復活）を反映した確定案です。</t>
+          <t>作成：令和8年9月3日／根拠：調査票 第1稿（0828版）＋調査票のレビューによる修正案＋調査報告書の骨子案／設問番号は調査票のレビューによる修正（ニーズ問7(7)の復活・在宅問13の復活）を反映した確定案です。</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>認定データとの紐付けが前提。事業対象者の判別には総合事業の対象者の情報も要る。該当数10未満の区分は統合（doc16 §6）</t>
+          <t>認定データとの紐付けが前提。事業対象者の判別には総合事業の対象者の情報も要る。該当数10未満の区分は統合（個人情報取扱管理ルール6）</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>在宅調査のみ。名簿に要支援の方は含まれない（doc43）ため2区分に統一</t>
+          <t>在宅調査のみ。名簿に要支援の方は含まれない（対象者名簿の確認による）ため2区分に統一</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
     <row r="48" ht="24" customHeight="1">
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>※ ★印は分析編（doc24 第Ⅱ部）で中心的に用いる設問・クロス表です。</t>
+          <t>※ ★印は調査報告書の分析編（第Ⅱ部）で中心的に用いる設問・クロス表です。</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>★doc23§4-1で削除を提案。問3(1)(7)(8)と役割が重複</t>
+          <t>★調査票のレビューで削除を提案。問3(1)(7)(8)と役割が重複</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J51" s="14" t="inlineStr">
         <is>
-          <t>★参加。担い手推計の中核（doc24§7-2）</t>
+          <t>★参加。担い手推計の中核（調査報告書の分析編）</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>★参加。担い手推計の中核（doc24§7-2）</t>
+          <t>★参加。担い手推計の中核（調査報告書の分析編）</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="J61" s="14" t="inlineStr">
         <is>
-          <t>★doc23§1-2で採用を推奨。手引き図表9が「活動」の構成要素として明示</t>
+          <t>★調査票のレビューで採用を推奨。手引き図表9が「活動」の構成要素として明示</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>★個人因子。派生 D01。ICF分析の主軸（doc24§6-4）</t>
+          <t>★個人因子。派生 D01。ICF分析の主軸（調査報告書の分析編）</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>基準月＝令和8年8月（doc23§2-3）</t>
+          <t>基準月＝令和8年8月（調査票のレビューによる）</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>★doc23§2-1で復活を推奨。在宅医療・介護連携の唯一の把握手段</t>
+          <t>★調査票のレビューで復活を推奨。在宅医療・介護連携の唯一の把握手段</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>★＝doc24 第Ⅱ部（分析編）の中核。X-01・X-02・X-03・X-04 は第2回策定委員会の資料の骨格になります。　｜　分母は表ごとに明記し、回収票の総数では割りません。「両設問」＝行・列の双方に回答した票を分母とします。</t>
+          <t>★＝調査報告書 第Ⅱ部（分析編）の中核。X-01・X-02・X-03・X-04 は第2回策定委員会の資料の骨格になります。　｜　分母は表ごとに明記し、回収票の総数では割りません。「両設問」＝行・列の双方に回答した票を分母とします。</t>
         </is>
       </c>
     </row>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>★分析編の中核。doc24§6-4 表5-X</t>
+          <t>★分析編の中核。調査報告書 表5-X</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>★議事録の「元気な軽度者」の検証。doc24§6-4 表5-Y</t>
+          <t>★議事録の「元気な軽度者」の検証。調査報告書 表5-Y</t>
         </is>
       </c>
     </row>
@@ -7767,7 +7767,7 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>★担い手の推計。doc24§7-2</t>
+          <t>★担い手の推計。調査報告書の分析編</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>★孤立層の特定。doc24§7-1</t>
+          <t>★孤立層の特定。調査報告書の分析編</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
-          <t>★施設の潜在需要。doc24§5-3</t>
+          <t>★施設の潜在需要。調査報告書 第4章</t>
         </is>
       </c>
     </row>

--- a/output/07_北塩原村第10期_集計仕様書.xlsx
+++ b/output/07_北塩原村第10期_集計仕様書.xlsx
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>20件。リスク判定・合成変数の定義</t>
+          <t>22件。リスク判定・合成変数の定義</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>20件。分析編で作成するクロス表</t>
+          <t>22件。分析編で作成するクロス表</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -6910,7 +6910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7508,32 +7508,32 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>AGE</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>年齢階級</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>名簿</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>65〜74歳／75〜84歳／85歳以上</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>集計軸</t>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Z01</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>入所の必要性の3区分</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>A票 問6・問12・問14、B票 問10</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>③入所が必要＝問6で「申請済み」。または問6で「検討中」かつ、B票 問10で「続けていくのは難しい」もしくは問14で家族・親族の介護が週4回以上あってなお検討中【要確認】。②支援を強めれば続けられる＝問6で「検討中」のうち③に当たらない方。①在宅で続けられる＝問6で「検討していない」。素案5-4(13)の3区分に対応する。該当数が10未満の区分は統合して示す</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>合成</t>
         </is>
       </c>
     </row>
@@ -7543,25 +7543,85 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
+          <t>Z02</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>村内施設の需要の2区分</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>A票 問6・問6-1</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>顕在需要＝問6で「申請済み」または「検討中」かつ問6-1で「入所・入居したい」。潜在需要＝問6で「検討していない」かつ問6-1で「入所・入居したい」。素案5-4(13)の把握の方法1に対応する。クロス表はX-15</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>合成</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>AGE</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>年齢階級</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>名簿</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>65〜74歳／75〜84歳／85歳以上</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>集計軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
           <t>CERT</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>認定状況</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>認定データ・総合事業の対象者情報</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>認定なし／事業対象者／要支援1・2／要介護1以上（4区分）。ニーズ調査の対象は一般高齢者・事業対象者・要支援認定者のため要介護1以上は少数</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>集計軸</t>
         </is>
@@ -7582,7 +7642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8444,6 +8504,86 @@
       <c r="H23" s="14" t="inlineStr">
         <is>
           <t>在宅医療・介護連携</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>X-21</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>入所の必要性の3区分 × 要介護度</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Z01</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>I（2区分）</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>在宅</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>Z01が算出できる票（問6に回答し、③の判定に用いる設問にも回答した票）</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>★必要利用定員総数の設定（素案5-4(6)(8)(13)）。③の規模が定員の判断の材料になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>X-22</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>入所の必要性の3区分 × 村内施設があれば</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>Z01</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>A票 問6-1</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>在宅</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>両設問（Z01が算出でき、かつ問6-1に回答した票）</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>★村内に整備した場合に受け止められる規模。③のうち村内であれば入所したい方が、村内整備の需要に当たる（素案5-4(13)・施策3-2）</t>
         </is>
       </c>
     </row>

--- a/output/07_北塩原村第10期_集計仕様書.xlsx
+++ b/output/07_北塩原村第10期_集計仕様書.xlsx
@@ -13,6 +13,7 @@
     <sheet name="派生変数" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="クロス集計定義" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="データレイアウト" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="精度管理" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ニーズ調査 集計一覧'!$A$3:$J$83</definedName>
@@ -59,7 +60,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +100,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -172,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -240,6 +246,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9070,4 +9082,963 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="2" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>入力データの精度管理（論理チェックとベリファイ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>集計を回す前に scripts/shukei_check.py を通し、鳴った件を1件ずつ原票に当たって直します。　｜　この表は実際に走る側（shukei_check.py）から生成しているため、点検の内容と本表は食い違いません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>■ 論理チェック（12項目）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>記号</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>いつ鳴るか</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>鳴ったときの直し方</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>白票</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>区分が「必須」の設問がすべて無回答</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>有効回答から外す。外した件数を回収数とは別に記録する</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>必須設問の無回答</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>区分が「必須」の設問が無回答（白票を除く）</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>原票に当たる。原票でも空欄なら無回答のまま集計する（基本方針7）</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>選択肢の範囲外</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>単一回答の値が、コードブックの選択肢にない（選択肢が1つ以下の設問は判定を省く。C02 を先に直す）</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>入力の誤り。原票に当たって直す</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>L04</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>単一回答に複数の印</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>単一回答の列に区切り文字を含む値が入っている</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>原票に当たる。原票で複数に印があれば「無回答」とする（基本方針8）</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>L05</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>複数回答の上限超え</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>「3つまで」と定めた設問で4つ以上が選ばれている</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>原票に当たる。原票でも上限を超えていれば、そのまま集計し件数を記録する</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>L06</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>答えるべきなのに無回答</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>分岐の親の条件を満たすのに、子の設問がすべて無回答</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>原票に当たる。回答者が飛ばしたのであれば無回答のまま</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>L07</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>答えるべきでないのに回答</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>分岐の親の条件を満たさないのに、子の設問に回答がある</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>原票に当たる。入力の誤りでなければ、親の回答の誤りを疑う</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>数値の範囲外</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>数値の設問が、定めた範囲の外にある</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>原票に当たって直す</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>L09</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>管理番号の不備</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>管理番号が空、または同じ番号が2件以上ある</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>重複は L09 で挙げ、重複回答の排除（Ⅰ-36）で扱う</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>名簿にない管理番号</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>対象者名簿にない管理番号</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>名簿は個人情報のため、照合は件数と番号の集合のみで行う</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>認定データとの矛盾</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>認定状況が「認定なし」なのに要介護度が入っている等</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>要介護認定データの受領後に実施する（Ⅰ-37）</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>直線回答（参考）</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>4択以上の単一回答で、同じ選択肢番号が10問以上続いている（2択が連なる箇所は偶然でも続くため数えない）</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>誤りとは限らない。自由記述とあわせて見て、無効とするかを判断する</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>■ コードブックの点検（5項目）　論理チェックは設問の番号・選択肢・分岐をコードブックから引くため、コードブックが壊れていれば鳴った件はデータの誤りではありません。先にここを見ます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>記号</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>いつ鳴るか</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>直し方</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>変数の重複</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>同じ変数が2件以上定義されている</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>調査票に当たってどちらが正しいかを決め、片方を消す</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>単一回答の選択肢が足りない</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>単一回答なのに選択肢が1つ以下（調査票から拾えていない疑い）</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>調査票の表を見て OVERRIDES に書く。直すまで L03 の判定は省く</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>複数回答の列と選択肢が合わない</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>複数回答の列の数が選択肢の数と違う</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>選択肢を数え直す。列は選択肢ごとに1つ</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>分岐の参照先がない</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>BRANCH に書いた親または子の変数がコードブックにない</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>設問番号の振り直しを疑う。BRANCH を直す</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>上限・範囲の参照先がない</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>LIMIT の変数、または RANGE の列がコードブックにない</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>LIMIT・RANGE を直す。参照先がないと L05・L08 は何も見ない</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>■ 分岐の規則（5件）　親が無回答のときはどちらとも言えないため鳴らせません。マトリクス設問の親（ニーズ 問5(1)・在宅A 問9）はデータの列を持たないため対象外です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>票</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>親</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>子を答える条件</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>子</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>根拠（調査票の指示）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>ニーズ</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>N_問1_2</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>2・3</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>N_問1_2_1</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>問1(2)で「1．必要ない」以外の方のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>ニーズ</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>N_問1_2</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>N_問1_2_2</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>問1(2)で「3．現在受けている」の方のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>ニーズ</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>N_問3_6</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>1・3</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>N_問3_6_2</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>問3(6)で入れ歯を利用の方のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>在宅A</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>ZA_問8</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>ZA_問10</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>問8で「2．利用していない」の方のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>在宅B</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>ZB_問7</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>1・2</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>ZB_問8</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>問7で「1．」「2．」の方のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>■ 複数回答の上限と数値の範囲</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>変数・列</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>とりうる値</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>複数回答の上限</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>ZB_問6</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>3個まで</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>上限を超えた件はL05。原票でも超えていればそのまま集計し件数を記録</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>複数回答の上限</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>ZB_問9</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>3個まで</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>上限を超えた件はL05。原票でも超えていればそのまま集計し件数を記録</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>数値の範囲</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>N_問3_1_体重</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>25〜150</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>範囲の外はL08。欠測として扱い件数を記録（身長・体重は1問が2列）</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>数値の範囲</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>N_問3_1_身長</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>100〜200</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>範囲の外はL08。欠測として扱い件数を記録（身長・体重は1問が2列）</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>数値の範囲</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>N_問8_2</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>0〜10</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>範囲の外はL08。欠測として扱い件数を記録（身長・体重は1問が2列）</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>■ ベリファイ（再入力による照合）　全件を二重入力する余力はないため、層の判定に効くものを全件、そうでないものを抽出とします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>区分が「必須」の設問</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>全件を二重入力して照合</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>単純集計の中心であり、無回答の扱いが報告書の全図表に及ぶ</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>派生変数に使う設問（R01〜R10・L01・S01・S02）</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>全件を二重入力して照合</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>資料3の3-3（元気な軽度者）・3-4（生活機能からみた4つの層）・3-6（担い手の可能性）の基礎。1件の誤りが層の人数を動かし、基本理念・基本目標の判断材料が狂う</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr"/>
+      <c r="E45" s="22" t="inlineStr"/>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>上記以外（オプション・村独自）</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>10パーセントを抽出して照合</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>構成比に効くが層の判定には使わない。抽出で誤りが見つかった設問は全件に広げる</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr"/>
+      <c r="E46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>ウェブ回答</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>対象外（入力を経ない）</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>ただし取込の件数がフォームの回答数と一致することを確かめる</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="inlineStr"/>
+      <c r="E47" s="22" t="inlineStr"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>・照合の結果は「入力の誤りの件数 ÷ 照合した項目数」として記録し、報告書に記載します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>■ コードブックの版（重要）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>・コードブックは令和8年9月4日版の調査票から作られています。実際に配られたのは9月9日の校了版です（doc34 §4）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="23" t="inlineStr">
+        <is>
+          <t>・版が違うと、鳴るべきものが鳴らず、鳴らなくてよいものが鳴ります。このため shukei_check.py は版を確かめ、食い違っていれば止まります（承知のうえで動かすときは --暫定）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>・校了版の調査票（Word）を受領してコードブックを作り直すまで、論理チェックの結果は暫定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>・9月4日版から作ったコードブックには7件の不備が残っています（C01 ZB_問8の重複／C02 ニーズ問3(10)・在宅A問5・問8・問14・在宅B問7の選択肢／C03 ニーズ問7(10)の列数）。いずれも作り直しで同時に解消します。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/07_北塩原村第10期_集計仕様書.xlsx
+++ b/output/07_北塩原村第10期_集計仕様書.xlsx
@@ -9090,13 +9090,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="64" customWidth="1" min="3" max="3"/>
-    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="2" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>管理番号が空、または同じ番号が2件以上ある</t>
+          <t>管理番号が空、同じ番号が2件以上ある、または票の形式（ニーズ＝数字のみ／在宅＝英字＋数字）に合わない。突合は全角・小文字・ハイフン・先頭の0を正規化してから行う</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -9988,56 +9988,410 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>■ 重複回答の排除（仕様書4Ⅰ(2)。第10期からの新規要件）　大事なのは「一意に定まること」である。同じ管理番号で2件あったとき、どちらを採るかが実行のたびに変われば回収数も構成比も変わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>段</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>採る方</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>有効票を採る（白票は採らない）</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>白票（必須設問がすべて無回答。shukei_check L01）は集計に用いない</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr"/>
+      <c r="E53" s="9" t="inlineStr"/>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>受け付けが後のものを採る</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>回答者が出し直した場合、後のものが訂正の意図によるとみられる</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr"/>
+      <c r="E54" s="22" t="inlineStr"/>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>同じ日ならウェブを採る</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>ウェブは入力を経ないため、入力の誤りが入らない</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr"/>
+      <c r="E55" s="9" t="inlineStr"/>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>回答した設問が多いものを採る</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>情報量の多いほうを残す</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="inlineStr"/>
+      <c r="E56" s="22" t="inlineStr"/>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>それでも並ばなければ回答の中身の並びで決める</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>読み込んだ順序で決めると、実行のたびに結果が変わりうる</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr"/>
+      <c r="E57" s="9" t="inlineStr"/>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>記号</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>何が起きているか</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>どう扱うか</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>紙が2件</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>同じ管理番号の紙の回答が2件以上ある</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>同一人が2枚返した（予備票）か、入力の重複。採否の順序で1件に絞る</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>紙とウェブ</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>同じ管理番号で紙とウェブの回答がある</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>仕様書4Ⅰ(2)が想定している重複。採否の順序で1件に絞る</t>
+        </is>
+      </c>
+      <c r="E61" s="22" t="inlineStr"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>ウェブが2件</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>同じ管理番号のウェブの回答が2件以上ある</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>フォームの二度押しまたは再送信。採否の順序で1件に絞る</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>管理番号が空</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>管理番号が入っていない（ウェブで入れ忘れた等）</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>回答は残す。名簿と突合できないため属性のクロスには入れない。空どうしの重複は見つけられないため件数を記録する</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="inlineStr"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>管理番号の形が違う</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>正規化しても票の形式（ニーズ＝数字のみ／在宅＝英字＋数字）に合わない</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>原票に当たって直す。直らなければ D4 と同じ扱いとする</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>名簿にない管理番号</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>正規化後の管理番号が対象者名簿にない</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>原票に当たって直す。直らなければ回答は残し、属性のクロスには入れない</t>
+        </is>
+      </c>
+      <c r="E65" s="22" t="inlineStr"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>名簿の番号が正規化で重なる</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>名簿の2つの管理番号が、正規化すると同じ値になる</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>先頭の0を落とす規則が使えない。正規化の規則を見直すまで突合を行わない</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr"/>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="23" t="inlineStr">
+        <is>
+          <t>・管理番号は正規化してから突き合わせる（全角→半角・区切りを除く・英字を大文字に・先頭の0を落とす）。論理チェックのL09と同じ規則を使う。規則が2か所に分かれると、点検は「重複なし」と言い、排除は1件落とす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="23" t="inlineStr">
+        <is>
+          <t>・管理番号の形式は、ニーズ調査が数字のみ、在宅介護実態調査が英字＋数字である（doc43 §2-4）。在宅の頭の英字を打ち間違えた場合は形式としては正しいままであり、名簿との突合（D6）でしか拾えない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="23" t="inlineStr">
+        <is>
+          <t>・管理番号が空・形式違い・名簿にない回答も捨てない。単純集計には入れ、属性のクロス（軸B 地区・軸C 年齢・軸D 性別・軸E 認定状況）には入れられない件数を記録する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="23" t="inlineStr">
+        <is>
+          <t>・管理番号が空の回答どうしの重複は機械では見つけられない。件数を報告書に明記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="23" t="inlineStr">
+        <is>
+          <t>・2つの名簿に重複する2人（doc43 §2-3）は重複回答ではない。調査ごとに1件として数え、2つの調査を合わせて1人を数える表は作らない。扱いは村のご確認事項（優先度S）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>・ウェブ回答はベリファイの対象外であるため、取込の件数がフォームの回答数と一致することを必ず確かめる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="25" t="inlineStr">
         <is>
           <t>■ コードブックの版（重要）</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="23" t="inlineStr">
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="23" t="inlineStr">
         <is>
           <t>・コードブックは令和8年9月4日版の調査票から作られています。実際に配られたのは9月9日の校了版です（doc34 §4）。</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="26" customHeight="1">
-      <c r="A53" s="23" t="inlineStr">
+    <row r="77" ht="26" customHeight="1">
+      <c r="A77" s="23" t="inlineStr">
         <is>
           <t>・版が違うと、鳴るべきものが鳴らず、鳴らなくてよいものが鳴ります。このため shukei_check.py は版を確かめ、食い違っていれば止まります（承知のうえで動かすときは --暫定）。</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="23" t="inlineStr">
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="23" t="inlineStr">
         <is>
           <t>・校了版の調査票（Word）を受領してコードブックを作り直すまで、論理チェックの結果は暫定です。</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="23" t="inlineStr">
+    <row r="79" ht="26" customHeight="1">
+      <c r="A79" s="23" t="inlineStr">
         <is>
           <t>・9月4日版から作ったコードブックには7件の不備が残っています（C01 ZB_問8の重複／C02 ニーズ問3(10)・在宅A問5・問8・問14・在宅B問7の選択肢／C03 ニーズ問7(10)の列数）。いずれも作り直しで同時に解消します。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A53:E53"/>
+  <mergeCells count="20">
+    <mergeCell ref="A77:E77"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A73:E73"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A75:E75"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A68:E68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/07_北塩原村第10期_集計仕様書.xlsx
+++ b/output/07_北塩原村第10期_集計仕様書.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="方針・凡例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ニーズ調査 集計一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="在宅調査 集計一覧" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="派生変数" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="クロス集計定義" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="データレイアウト" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="精度管理" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方針・凡例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ニーズ調査 集計一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="在宅調査 集計一覧" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="派生変数" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クロス集計定義" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="データレイアウト" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="精度管理" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ニーズ調査 集計一覧'!$A$3:$J$83</definedName>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>22件。リスク判定・合成変数の定義</t>
+          <t>23件。リスク判定・合成変数の定義</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -1383,7 +1383,7 @@
     <row r="47" ht="24" customHeight="1">
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>※ 派生変数のリスク判定の該当基準には【要確認】を付しています。手引きに明記があるのはBMI 18.5以下のみで、他は見える化システムの算出方法との突合が必要です（確認事項K-91）。</t>
+          <t>※ 派生変数のリスク判定の該当基準は、「介護予防・日常生活圏域ニーズ調査 実施の手引き」（第10期用。Q34〜Q37・参考資料2）によります。同手引きに該当基準の記載がないR07・R08・R09には【当方の定義】を付しています。これらは老研式活動能力指標の区分に準じたものであり、見える化システムの全国・県の値とは比べません。</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>個人因子。派生 R04。18.5以下で低栄養が疑われる（手引き明記）</t>
+          <t>個人因子。派生 R04・R04S。18.5以下で低栄養が疑われる（手引きQ36）</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6980,300 +6980,300 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>R01</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>運動器の機能低下</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>問2(1)(2)(3)</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>3項目のうち「3．できない」が2項目以上で該当【要確認】</t>
-        </is>
-      </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>問2(1)〜(5)</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>5項目のうち3項目以上で該当。該当の選択肢は(1)(2)(3)が「3．できない」、(4)が「1．何度もある」「2．1度ある」、(5)が「1．とても不安である」「2．やや不安である」（手引きQ34）</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>リスク判定</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>R02</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>転倒リスク</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>問2(4)(5)</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="inlineStr">
-        <is>
-          <t>(4)で「1．何度もある」または「2．1度ある」で該当【要確認】</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>問2(4)</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>「1．何度もある」または「2．1度ある」で該当（手引き参考資料2）</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>リスク判定</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>R03</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>閉じこもり傾向</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>問2(6)(7)(8)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>(6)で「1．ほとんど外出しない」または「2．週1回」で該当【要確認】</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>問2(6)</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>「1．ほとんど外出しない」または「2．週1回」で該当（手引き参考資料2）</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>リスク判定</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="17" t="n">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>R04</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>低栄養の傾向</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>問3(1)</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>BMI 18.5以下で該当（低栄養が疑われる高齢者。手引きQ36）</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>リスク判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>R04S</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>低栄養状態</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>問3(1)(7)</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>BMI 18.5以下（手引き明記）または(7)で「1．はい」で該当【要確認】</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>BMI 18.5以下かつ(7)「1．はい」で該当（低栄養状態にある高齢者。手引きQ36）。R99には数えない</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>リスク判定</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>R05</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>口腔機能の低下</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>問3(2)(3)(4)(6)①</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>(2)(3)(4)のうち2項目以上「1．はい」で該当【要確認】</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>問3(2)(3)(4)</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>3項目のうち2項目で該当（手引きQ35）</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>リスク判定</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>R06</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>認知機能の低下</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>問4(1)(2)(3)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>(1)「1．はい」／(2)「2．いいえ」／(3)「1．はい」のいずれかで該当【要確認】</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>問4(1)</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>「1．はい」で該当（手引きQ37）</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>リスク判定</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>R07</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>IADLの低下</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>問4(4)〜(8)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>5項目のうち「3．できない」が1項目以上で該当【要確認】</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>5項目のうち「3．できない」が1項目以上で該当【当方の定義】手引きに該当基準の記載がなく、老研式活動能力指標の手段的自立に準じた</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>リスク判定</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>R08</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>知的能動性の低下</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>問4(10)(11)(12)</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>3項目すべて「2．いいえ」で該当【要確認】</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>3項目すべて「2．いいえ」で該当【当方の定義】手引きに該当基準の記載がない</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>リスク判定</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>R09</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>社会的役割の低下</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>問4(13)〜(16)</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>4項目すべて「2．いいえ」で該当【要確認】</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>リスク判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>うつ傾向</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>問8(3)(4)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>いずれか「1．はい」で該当【要確認】</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>4項目すべて「2．いいえ」で該当【当方の定義】手引きに該当基準の記載がない</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>リスク判定</t>
         </is>
@@ -7285,27 +7285,27 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>R99</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>リスク該当領域数</t>
+          <t>うつ傾向</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>R01〜R10</t>
+          <t>問8(3)(4)</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>該当したリスクの個数（0〜10）。3区分（0／1〜2／3以上）にも変換</t>
+          <t>いずれか「1．はい」で該当（手引き参考資料2）</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>合成</t>
+          <t>リスク判定</t>
         </is>
       </c>
     </row>
@@ -7315,22 +7315,22 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>R99</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>疾病数</t>
+          <t>リスク該当領域数</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>問8(7)</t>
+          <t>R01〜R10</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>選択された疾病の数（「1．ない」は0）。3区分（0／1〜2／3以上）にも変換</t>
+          <t>該当したリスクの個数（0〜10）。3区分（0／1〜2／3以上）にも変換</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
@@ -7345,22 +7345,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>社会参加あり</t>
+          <t>疾病数</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>問5(1)</t>
+          <t>問8(7)</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>8種類のいずれかに「月1〜3回」以上参加で該当</t>
+          <t>選択された疾病の数（「1．ない」は0）。3区分（0／1〜2／3以上）にも変換</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -7375,22 +7375,22 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>支え合いの受領あり</t>
+          <t>社会参加あり</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>問7(1)(3)</t>
+          <t>問5(1)</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>いずれかで「そのような人はいない」以外を選択で該当</t>
+          <t>8種類のいずれかに「月1〜3回」以上参加で該当</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
@@ -7405,17 +7405,17 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>支え合いの提供あり</t>
+          <t>支え合いの受領あり</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>問7(2)(4)</t>
+          <t>問7(1)(3)</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -7435,22 +7435,22 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>孤立</t>
+          <t>支え合いの提供あり</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>S01・S02</t>
+          <t>問7(2)(4)</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>S01・S02がいずれも非該当で「孤立」</t>
+          <t>いずれかで「そのような人はいない」以外を選択で該当</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
@@ -7465,22 +7465,22 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>L01</t>
+          <t>S99</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>生活機能4層</t>
+          <t>孤立</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>R99・P01・認定状況</t>
+          <t>S01・S02</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>第1層＝R99が0かつP01該当／第2層＝R99が0かつP01非該当／第3層＝R99が1以上かつ認定なし（事業対象者を含む）／第4層＝認定あり</t>
+          <t>S01・S02がいずれも非該当で「孤立」</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -7495,85 +7495,85 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>生活機能4層</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>R99・P01・認定状況</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>第1層＝R99が0かつP01該当／第2層＝R99が0かつP01非該当／第3層＝R99が1以上かつ認定なし（事業対象者を含む）／第4層＝認定あり</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>合成</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
           <t>B01</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>BMI</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>問3(1)</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>体重kg÷（身長m）^2。小数第1位まで</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>合成</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Z01</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>入所の必要性の3区分</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>A票 問6・問12・問14、B票 問10</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>③入所が必要＝問6で「申請済み」。または問6で「検討中」かつ、B票 問10で「続けていくのは難しい」もしくは問14で家族・親族の介護が週4回以上あってなお検討中【要確認】。②支援を強めれば続けられる＝問6で「検討中」のうち③に当たらない方。①在宅で続けられる＝問6で「検討していない」。素案5-4(13)の3区分に対応する。該当数が10未満の区分は統合して示す</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>合成</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>Z02</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>村内施設の需要の2区分</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>A票 問6・問6-1</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>顕在需要＝問6で「申請済み」または「検討中」かつ問6-1で「入所・入居したい」。潜在需要＝問6で「検討していない」かつ問6-1で「入所・入居したい」。素案5-4(13)の把握の方法1に対応する。クロス表はX-15</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>合成</t>
         </is>
@@ -7585,27 +7585,27 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>AGE</t>
+          <t>Z02</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>年齢階級</t>
+          <t>村内施設の需要の2区分</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>名簿</t>
+          <t>A票 問6・問6-1</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>65〜74歳／75〜84歳／85歳以上</t>
+          <t>顕在需要＝問6で「申請済み」または「検討中」かつ問6-1で「入所・入居したい」。潜在需要＝問6で「検討していない」かつ問6-1で「入所・入居したい」。素案5-4(13)の把握の方法1に対応する。クロス表はX-15</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>集計軸</t>
+          <t>合成</t>
         </is>
       </c>
     </row>
@@ -7615,25 +7615,55 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
+          <t>AGE</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>年齢階級</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>名簿</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>65〜74歳／75〜84歳／85歳以上</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>集計軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
           <t>CERT</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>認定状況</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>認定データ・総合事業の対象者情報</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>認定なし／事業対象者／要支援1・2／要介護1以上（4区分）。ニーズ調査の対象は一般高齢者・事業対象者・要支援認定者のため要介護1以上は少数</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>集計軸</t>
         </is>
